--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_elk_bull_limited_entry.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_elk_bull_limited_entry.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +47,13 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,8 +70,23 @@
         <fgColor rgb="004F2D1D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE5D7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,11 +108,25 @@
         <color rgb="00D8B58E"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C58F61"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C58F61"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C58F61"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C58F61"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -108,6 +142,36 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,1342 +561,1342 @@
   <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>OBJECTID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>boundary_name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>hunt_type</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>SHAPE__Area</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>SHAPE__Length</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>permits_2026_res</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>permits_2026_nr</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>permits_2026_total</t>
         </is>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>Grand County—Boundary begins at the Steer Ridge road at Ten Mile Knoll and the Book Cliffs summit (north-south drainage divide); southwest along the Book Cliffs summit on Diamond Ridge to the Uintah and Ouray Indian Reservation boundary (Hells Hole/head of Sego Canyon); north on this boundary (west side of West Willow Creek) to the DWR Wildlife Management Area/Ute Tribe Fence at the confluence of East and West Willow Creek; northeast from this confluence; cross-country to the Steer Ridge road (NW 1/4 Sec 7, T17S R21E); south and east on the Steer Ridge road (atop the drainage divide) to Ten Mile Knoll and the Book Cliffs summit. EXCLUDES ALL NATIVE AMERICAN TRUST LAND WITHIN THIS BOUNDARY. Excludes all CWMUs. USGS 1:100,000 Maps: Westwater. Boundary questions? Call Vernal office, 435-781-9453. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>385796584.800781</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>96989.9945012105</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
+      <c r="I2" s="13" t="inlineStr"/>
+      <c r="J2" s="12" t="inlineStr"/>
+      <c r="K2" s="13" t="inlineStr"/>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Cache, Meadowville</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Rich County—Boundary begins at US-89 and the USFS boundary west of Garden City; south along this USFS boundary to SR-39; east on SR-39 to SR-16; north on SR-16 to SR-30; northwest on SR-30 to US-89; west on US-89 to the USFS boundary. USGS 1:100,000 Maps: Logan, Ogden. This hunt is comprised of all or largely private property. Hunters should acquire written permission from the landowner before applying for this hunt. Boundary questions? Call the Ogden office, 801-476-2740.  - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>1326877011.01172</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>215736.623473059</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
+      <c r="J3" s="14" t="inlineStr"/>
+      <c r="K3" s="15" t="inlineStr"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Manti</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Carbon, Emery, Sanpete, Sevier and Utah counties—Boundary begins at the junction of US-6 and US-89 in Spanish Fork Canyon; southeast on US-6 to Price and SR-10; south on SR-10 to I-70; west on I-70 to US-89; north on US-89 to US-6 in Spanish Fork Canyon. USGS 1:100,000 Maps: Nephi, Price, Huntington, Manti, Salina. Boundary questions? Call the Springville office, 801-491-5678 or the Price office, 435-613-3700. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>11128638731.375</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>507808.90566063</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="I4" s="13" t="inlineStr"/>
+      <c r="J4" s="12" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Fillmore, Pahvant</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Millard and Sevier counties—Boundary begins at I-70 and I-15; north on I-15 to US-50 at Scipio; southeast on US-50 to Salina and US-89; south on US-89 to I-70; southwest on I-70 to I-15. EXCLUDES ALL NATIVE AMERICAN TRUST LANDS WITHIN THIS BOUNDARY.  Excludes all CWMUs. USGS 1:100,000 Maps: Delta, Richfield, Salina. Boundary questions? Call the Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>3631412763.55469</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>296587.682619706</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="I5" s="15" t="inlineStr"/>
+      <c r="J5" s="14" t="inlineStr"/>
+      <c r="K5" s="15" t="inlineStr"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Grand County—Boundary begins at the Colorado River and the Utah-Colorado state line; south on this state line to the Dolores River; northwest along this river to the Colorado River; northeast along this river to the Utah-Colorado state line. Excludes all CWMUs. USGS 1:100,000 Maps: Moab, Westwater. Boundary questions? Call Price office, 435-613-3700. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>783319924.929688</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>174586.911461462</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Morgan-South Rich</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Morgan, Rich, Summit and Weber counties—Boundary begins at I-80 and the Utah-Wyoming state line; west on I-80 to Echo Junction and I-84; west on I-84 to SR-167 at Mountain Green (Trappers Loop Road); north along SR-167 to SR-39; east along SR-39 to Woodruff and SR-16; southeast on SR-16 to the Utah-Wyoming state line; south along the state line to I-80. Excludes all CWMUs. This hunt is comprised of all or largely private property.  Hunters should acquire written permission from the landowner before applying for this hunt. USGS 1:100,000 Maps: Logan, Ogden. Boundary questions? Call the Ogden office, 801-476-2740. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>4269238003.40625</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>299901.108953191</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr"/>
+      <c r="J7" s="14" t="inlineStr"/>
+      <c r="K7" s="15" t="inlineStr"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>North Slope, Three Corners</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Daggett County—Boundary begins at the Flaming Gorge Reservoir main channel western shoreline on the east side of Lucerne Point at the Utah-Wyoming state line; east on this state line to the Utah-Colorado state line; south on this state line to the Green River; west along this river to the Flaming Gorge Reservoir west shoreline; west along this shoreline to the Utah-Wyoming state line; east along the state line to Lucerne Point; east around Lucerne Point to the Utah-Wyoming State line. Excludes all CWMUs. USGS 1:100,000 Maps: Dutch John. Boundary questions? Call Vernal office, 435-781-9453. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>1023344833.11719</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>281220.992173911</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="12" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Emery, Piute, Sevier and Wayne counties—Boundary begins at I-70 and SR-24 north of Sigurd; south and east on SR-24 to the Caineville Wash road; north on this road to the Cathedral Valley road; west on this road to Rock Springs Bench and the Last Chance Desert road; north on this road to the Blue Flats road; north and east on this road to the Willow Springs road; north on this road towards Windy Peak and the Windy Peak road; west on this road to SR-72; north on SR-72 to I-70; west on I-70 to SR-24 north of Sigurd. EXCLUDES ALL NATIONAL PARKS. USGS 1:100,000 Maps: Loa, Salina. Boundary questions? Call the Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>5062000544.74219</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>377635.595733982</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
+      <c r="I9" s="15" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>San Juan Bull Elk</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Grand and San Juan counties—Boundary begins at the confluence of the San Juan and Colorado rivers; north along the Colorado River to Kane Springs Creek; southeast along this creek to Hatch Wash; southeast along this wash to US-191; south on US-191 to the Big Indian road; east and north on this road to the Lisbon Valley road; southeast on this road to the Island Mesa road; east on this road to the Utah-Colorado state line; south on this state line to US-491; west on US-491 to US-191; south on US-191 to the San Juan River; west on this river to the Colorado River. EXCLUDES ALL NATIVE AMERICAN TRUST LANDS WITHIN THIS BOUNDARY. EXCLUDES ALL NATIONAL PARKS. EXCLUDES ALL CWMUs. USGS 1:100,000 Maps: Blanding, La Sal, Hite Crossing, Bluff. Boundary questions? Call the Price office, 435-613-3700. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>18111053793.7852</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>1042871.86610327</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Diamond Mtn</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Daggett and Uintah counties—Boundary begins at the Utah-Colorado state line and the Green River at Browns Park; west along this river to Gorge Creek; south along Gorge Creek to the USFS/private land boundary at the head of Davenport Draw; south along the USFS/private land boundary on the west side of Davenport Draw to the BLM boundary; south along the BLM boundary approximately one-third of a mile to the rim of Diamond Mountain; south and easterly along this rim until the rim intersects the Diamond Mountain road (Jones Hole Road); south and west on this road to the Brush Creek road; south on this road to the Island Park/Rainbow Park road; east on this road to the Dinosaur National Monument boundary; north and east on this boundary to the Utah-Colorado state line; north on this state line to the Green River. Excludes all CWMUs. USGS 1:100,000 Maps: Dutch John. Boundary questions? Call Vernal office, 435-781-9453. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>1877174012.56641</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>232645.557250317</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="I11" s="15" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Wasatch Mtns</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Carbon, Duchesne, Summit, Utah and Wasatch counties-Boundary begins at the junction of I-15 and 12300 south in Salt Lake; east on this road to 700 East; south on this road to Pioneer road: east on this road to Highland Drive; south on this road to Upper Corner Canyon Road; east on this road to the Salt Lake/Utah county line; east on this county line to the Salt Lake/Wasatch county line; northeast on this county line to the Wasatch/Summit county line; east on this county line to US-40; south on US-40 to SR-32; east on SR-32 to SR-35; southeast on SR-35 to SR-87; south on SR-87 to Duchesne and US-191; south on US-191 to US-6; northwest on US-6 to I-15; north on I-15 to 12300 south in Salt Lake City. EXCLUDING ALL NATIVE AMERICAN TRUST LAND WITHIN THIS BOUNDARY. USGS 1:100,000 Maps: Duchesne, Nephi, Price, Provo, Salt Lake City. Boundary questions? Call the Springville office, 801-491-5678. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>11432463041.543</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>542023.765603494</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="12" t="inlineStr"/>
+      <c r="K12" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>West Desert, Deep Creek</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Juab and Tooele counties—Boundary begins at the Pleasant Valley road and the Utah-Nevada state line; north along this state line to the Salt Springs (Blue Lake) road; south on this road to the Pleasant Valley road; northwest on this road to the Utah-Nevada state line. EXCLUDES ALL NATIVE AMERICAN TRUST LAND WITHIN THIS BOUNDARY. Access is limited. USGS 1:100,000 Maps: Fish Springs, Wildcat Mountain. Boundary questions? Call the Springville office, 801-491-5678. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>2895146216.24219</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>308655.865864557</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="I13" s="15" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="15" t="inlineStr"/>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>East Canyon</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Davis, Morgan, Salt Lake and Summit counties—Boundary begins at Echo Junction and I-80; southwest along I-80 to I-15; north on I-15 to its junction with I-84 near Ogden; east on I-84 to Echo Junction. This hunt is comprised of all or largely private property. Hunters should acquire written permission from the landowner before applying for this hunt. USGS 1:100,000 Maps: Salt Lake City, Ogden. Boundary questions? Call the Ogden office, 801-476-2740. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>2864855080.24219</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>254046.203016068</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr"/>
+      <c r="K14" s="13" t="inlineStr"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Cache, North</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Cache, Box Elder and Rich counties—Boundary begins at US-91 and the Utah-Idaho state line; south on US-91 to US-89 in Logan; east and north on US-89 to the Utah-Idaho state line; west along this state line to US-91. USGS 1:100,000 Maps: Tremonton, Logan. Boundary questions? Call the Ogden office, 801-476-2740. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>1118747214.51953</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>177791.416717997</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="I15" s="15" t="inlineStr"/>
+      <c r="J15" s="14" t="inlineStr"/>
+      <c r="K15" s="15" t="inlineStr"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Cache, South</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Cache, Rich and Weber counties—Boundary begins at US-89 and the USFS boundary west of Garden City; south on this boundary to SR-39; southwest on SR-39 to USFS Road 054 (Ant Flat road); north on this road to SR-101; west on SR-101 to SR-165; north on SR-165 to US 89/91; north on US 89/91 to US-89; northeast on US-89 to the USFS boundary approximately 3 miles west of Garden City. USGS 1:100,000 Maps: Logan, Ogden. Boundary questions? Call the Ogden office, 801-476-2740. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>2005612808.37891</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>278707.212910171</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Grand and San Juan counties—Boundary begins at I-70 and the Green River; south along this river to the Colorado River; north along this river to Kane Springs Creek; southeast along this creek to Hatch Wash; southeast along this wash to US-191; south on US-191 to the Big Indian road; east on this road to the Lisbon Valley road; southeast on this road to the Island Mesa road; east on this road to the Utah-Colorado state line; north on this state line to the Dolores River; west along this river to the Colorado River; north along this river to the Utah-Colorado state line; north on this state line to I-70; west on I-70 to the Green River. Excludes all CWMUs. USGS 1:100,000 Maps: La Sal, Moab, San Rafael Desert, Westwater. Boundary questions? Call Price office, 435-613-3700. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>10529173059.2461</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>889527.467837135</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="I17" s="15" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="15" t="inlineStr"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Piute and Sevier counties—Boundary begins at US-89 and I-70 near Sevier; south on US-89 to SR-62; east and north on SR-62 to SR-24; north on SR-24 to I-70; south on I-70 to US-89 near Sevier. EXCLUDES ALL NATIVE AMERICAN TRUST LANDS WITHIN THIS BOUNDARY. USGS 1:100,000 Maps: Beaver, Loa, Richfield, Salina. Boundary questions? Call the Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>2924050244.56641</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>254264.107687356</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Garfield and Piute counties—Boundary begins at US-89 and SR-62; south on US-89 to SR-12; east on SR-12 to the Widtsoe-Antimony Road; north on this road to SR-22; north on SR-22 to SR-62; west on SR-62 to US-89. Excludes all CWMUs. USGS 1:100,000 Maps: Beaver, Escalante, Loa, Panguitch. Boundary questions? Call the Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>2750378126.48438</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>216681.844399342</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
+      <c r="I19" s="15" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="15" t="inlineStr"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Panguitch Lake</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Garfield, Iron and Kane counties—Boundary begins at US-89 and SR-14; north on US-89 to SR-20; west on SR-20 to I-15; south on I-15 to SR-14; east on SR-14 to US-89. USGS 1:100,000 Maps: Beaver, Cedar City, Panguitch. Boundary questions? Call the Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>3662190615.85938</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>275913.121495248</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr"/>
+      <c r="K20" s="13" t="inlineStr"/>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Box Elder, Pilot Mtn</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Box Elder and Tooele counties—Boundary begins at SR-30 and the Utah-Nevada state line; east on SR-30 to the township line between R15W and R16W; south on this line to I-80; west on I-80 to Pilot Creek Valley road; north along this road to SR-30; east on SR-30 to the Utah-Nevada state line. Elk hunters with this permit may hunt Nevada’s portion of this interstate unit (091) and abide by Nevada laws. USGS 1:100,000 Maps: Newfoundland Mtns., Bonneville Salt Flats, Wells, Wendover. Boundary questions? Call the Ogden office, 801-476-2740. Nevada hunt regulation questions? Call NDOW, (775) 777-2300.  - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>6104781593.0625</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>339736.049597248</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr"/>
+      <c r="I21" s="15" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="15" t="inlineStr"/>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Beaver, East</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Beaver, Garfield, Iron, Millard, Piute and Sevier counties—Boundary begins at I-15 and I-70; east on I-70 to US-89; south on US-89 to SR-20; west on SR-20 to I-15; north on I-15 to I-70. Excludes all CWMUs. USGS 1:100,000 Maps: Beaver, Panguitch, Richfield. Boundary questions? Call Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>3366846300.53516</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>270972.494133026</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr"/>
+      <c r="K22" s="13" t="inlineStr"/>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Box Elder, Grouse Creek</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Box Elder County—Boundary begins on the Utah-Idaho state line at the Lynn/Almo, Idaho road and the Utah-Idaho state line; southwest on this road through the Raft River Narrows to Lynn and the Lynn Valley road; south on this road to the Dove Creek road; southeast on this road over Dove Creek Pass to SR-30 near Rosette; south and west on SR-30 to the Utah-Nevada state line; north on this state line to the Utah-Idaho state line; east on this state line to the Lynn/Almo, Idaho road. This hunt is comprised of all or largely private property. Hunters should acquire written permission from the landowner before applying for this hunt. Excludes all CWMUs. USGS 1:100,000 Maps: Grouse Creek, Jackpot, Newfoundland Mountains, Wells. Boundary Questions? Call Ogden office, 801-476-2740. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>4071256208.98438</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>310152.460974788</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="I23" s="15" t="inlineStr"/>
+      <c r="J23" s="14" t="inlineStr"/>
+      <c r="K23" s="15" t="inlineStr"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Barney Top/Kaiparowits</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Garfield and Kane counties—Boundary begins SR-12 and the Paria River in Cannonville; south on the Paria river to US-89; east on US-89 to the Utah/Arizona border; east on the Utah/Arizona border to Lake Powell; east and north on Lake Powell to Bullfrog creek and the Notom Road; north on the Notom Road to the Burr Trail; west on the Burr Trail to Boulder and SR-12; west on SR-12 to Main Canyon-Sweetwater Road; west on Main Canyon-Sweetwater Road to John’s Valley Road; south on John’s Valley Road to SR-12; east on SR-12 to Cannonville and the Paria River. USGS 1:100,000 Maps: Escalante, Navajo Mountain, Smoky Mountain. Boundary questions? Call the Cedar City office, 435-865-6100 - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>13965654481.3516</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>610820.993789482</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="12" t="inlineStr"/>
+      <c r="K24" s="13" t="inlineStr"/>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Boulder Elk</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Garfield, Piute, Sevier and Wayne counties—Boundary begins at SR-24 and SR-62; south on SR-62 to SR-22; south on SR-22 to the Main Canyon-Sweetwater road; east on Main Canyon-Sweetwater road to SR-12; east on SR-12 to Boulder and the Burr Trail road; east on this road to the Notom road; north on this road to SR-24; west on SR-24 to SR-62. Excludes all CWMUs. USGS 1:100,000 Maps: Escalante, Loa, Panguitch, Salina. Boundary questions? Call Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>7750043502.70703</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>485457.518931418</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="I25" s="15" t="inlineStr"/>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="15" t="inlineStr"/>
     </row>
     <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Southwest Desert, North</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Beaver, Iron and Millard counties—Boundary begins at the Utah-Nevada state line and US-6/50; east on US-6/50 to SR-257; south on SR-257 to SR-21; west on SR-21 to the Utah-Nevada state line. Excludes all CWMUs. USGS 1:100,000 Maps: Beaver, Delta, Garrison, Richfield, Tule Valley, Wah Wah Mountains North, Wah Wah Mountains South, Wilson Creek Range. Boundary questions? Call the Cedar City office, 435-865-6100. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>10830041079.4258</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>492484.781548897</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="12" t="inlineStr"/>
+      <c r="K26" s="13" t="inlineStr"/>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Southwest Desert, South</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Beaver, Iron and Millard counties—Boundary begins at the Utah-Nevada state line and US-6/50; east on SR-21; south on SR-21 to SR-130; south on SR-130 to I-15; south on I-15 to SR-56; west on SR-56 to the Lund highway; northwest on this highway to Lund and the Union Pacific railroad tracks; southwest along these tracks to the Utah-Nevada state line; north on this state line to US-6/50. Excludes all CWMUs. USGS 1:100,000 Maps: Beaver, Caliente, Cedar City, Delta, Garrison, Richfield, Wah Wah Mountains - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>11219094968.6719</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>593571.278560212</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr"/>
+      <c r="I27" s="15" t="inlineStr"/>
+      <c r="J27" s="14" t="inlineStr"/>
+      <c r="K27" s="15" t="inlineStr"/>
     </row>
     <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/East</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Grand and Uintah counties—Boundary begins at the Utah-Colorado state line and the White River; west along this river to the Green River; south along this river to the southern boundary of the Ute Indian Reservation; east along this boundary to the Sego Canyon road; south on this road to the Thompson Canyon Road; south on this road to Thompson and I-70; east on I-70 to the Utah-Colorado state line; north on this state line to the White River.
 EXCLUDES THE BOOK CLIFFS, LITTLE CREEK ROADLESS UNIT. EXCLUDES ALL NATIVE AMERICAN TRUST LAND WITHIN THIS BOUNDARY. USGS 1:100,000 Maps: Huntington, Moab, Price, Seep Ridge, Vernal, Westwater. Boundary questions? Call the Vernal office, 435-781-9453 or the Price office, 435-613-3700. EXCLUDES Book Cliffs, Little Creek Roadless Unit as follows: Book Cliffs, Little Creek Roadless Grand County—Boundary begins at Steer Ridge road and Ten Mile Knoll; southwest along Diamond Ridge and the Book Cliffs summit (north-south drainage divide) to the Uintah and Ouray Indian Reservation boundary (Hells Hole/head of Sego Canyon); north along this boundary (west side of West Willow Creek) to the Wildlife Management Area/Ute Tribe Fence at the confluence of East and West Willow Creek; northeast to the west fork of the Steer Ridge road (NW 1/4 Sec 7, T17 S R 21 E); south and east along the Steer Ridge road (atop the drainage divide) to Ten Mile Knoll. EXCLUDES ALL NATIVE AMERICAN TRUST LAND WITHIN THIS BOUNDARY. USGS 1:100,000 Maps: Westwater. Boundary questions? Call the Vernal office, 435-781-9453. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>13307986739.6211</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>764624.689454227</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="12" t="inlineStr"/>
+      <c r="K28" s="13" t="inlineStr"/>
     </row>
     <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Nebo/San Pitch Mtns</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Juab, Millard, Sanpete, Sevier and Utah counties—Boundary begins at US-6 and I-15 at Spanish Fork; southeast on US-6 to US-89 near Thistle; south on US-89 to Big Hollow Rd; west on Big Hollow Rd to SR-132 in Fountain Green; South on SR-132 to Main St (SR-116) in Moroni; East on SR-116 to US-89 in Mount Pleasant; south on US-89 to SR-28 in Gunnison; north on SR-28 to I-15 in Nephi; north on I-15 to US-6 at Spanish Fork. Excludes all CWMUs. USGS 1:100,000 Maps: Maps: Delta, Manti, Nephi, Provo, Salina. Boundary questions? Call the Springville office, 801-491-5678. - A hunting permit does not authorize the permit holder to hunt on Native American trust lands, CWMUs (unless you specifically have a permit for that CWMU) or on National Park lands. Furthermore, it is the responsibility of hunters to learn if hunting is allowed and what specific rules and regulations may apply on National Monuments, National Wildlife Refuges, State Parks, UDWR Wildlife and Waterfowl Management areas, military installations and within the boundaries of cities, towns and municipalities. Written permission is required to hunt private lands.</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>4220789905.82813</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>363560.008955085</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="I29" s="15" t="inlineStr"/>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K29"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
